--- a/entertainment_forms/029_online_social_networking_questionnaire--entertainment_forms.xlsx
+++ b/entertainment_forms/029_online_social_networking_questionnaire--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>online-security</t>
+          <t>Online Social Networking Questionnaire Page 6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>online-security</t>
+          <t>Online Social Networking Questionnaire Page 8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>online-habits</t>
+          <t>Online Social Networking Questionnaire Page 13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'a'}</t>
+          <t>a</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'b'}</t>
+          <t>b</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'c'}</t>
+          <t>c</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'a'}</t>
+          <t>a</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'b'}</t>
+          <t>b</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'c'}</t>
+          <t>c</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'a'}</t>
+          <t>a</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'b'}</t>
+          <t>b</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'c'}</t>
+          <t>c</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
